--- a/data/launch/launch-readiness-checklist.xlsx
+++ b/data/launch/launch-readiness-checklist.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>P-RUI</t>
+          <t>Rui Bastos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>P-TOM</t>
+          <t>Tomas Silva</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>P-KOF</t>
+          <t>Kofi Adjei</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P-KOF</t>
+          <t>Kofi Adjei</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Resolution time claims checked against POL-10</t>
+          <t>Resolution time claims checked against POLICY-10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P-GAB</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>POL-10 permits tier table only</t>
+          <t>POLICY-10 permits tier table only</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>P-ANA</t>
+          <t>Ana Fialho</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -657,7 +657,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EXP-02</t>
+          <t>EXPERIMENT-02</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P-GAB</t>
+          <t>Gabriela Rocha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>P-RUI</t>
+          <t>Rui Bastos</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>INC-01 and INC-02 have no follow-up owner</t>
+          <t>INCIDENT-01 and INCIDENT-02 have no follow-up owner</t>
         </is>
       </c>
     </row>

--- a/data/launch/launch-readiness-checklist.xlsx
+++ b/data/launch/launch-readiness-checklist.xlsx
@@ -449,7 +449,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Launch readiness, Assist expansion</t>
+          <t>Launch readiness, the help portal expansion</t>
         </is>
       </c>
     </row>
